--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T15:12:43+00:00</t>
+    <t>2023-12-13T15:24:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T15:24:56+00:00</t>
+    <t>2023-12-13T15:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T15:28:34+00:00</t>
+    <t>2024-02-12T12:57:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T12:57:06+00:00</t>
+    <t>2024-02-12T12:59:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T12:59:31+00:00</t>
+    <t>2024-02-12T14:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:31:30+00:00</t>
+    <t>2024-02-12T16:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T16:33:03+00:00</t>
+    <t>2024-02-12T16:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T16:38:55+00:00</t>
+    <t>2024-02-12T16:39:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T16:39:27+00:00</t>
+    <t>2024-02-12T16:43:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot</t>
+    <t>1.0.1-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T16:43:27+00:00</t>
+    <t>2024-02-13T13:14:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T13:14:14+00:00</t>
+    <t>2024-02-14T14:30:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-14T14:30:45+00:00</t>
+    <t>2024-02-15T09:58:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T09:58:35+00:00</t>
+    <t>2024-02-15T09:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T09:59:20+00:00</t>
+    <t>2024-02-15T10:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T10:29:18+00:00</t>
+    <t>2024-02-15T10:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T10:48:09+00:00</t>
+    <t>2024-02-15T10:48:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T10:48:23+00:00</t>
+    <t>2024-02-15T10:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T10:53:05+00:00</t>
+    <t>2024-02-15T10:58:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T10:58:34+00:00</t>
+    <t>2024-02-15T11:00:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T11:00:02+00:00</t>
+    <t>2024-02-15T11:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T11:15:07+00:00</t>
+    <t>2024-02-15T11:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T11:15:53+00:00</t>
+    <t>2024-02-15T12:51:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T12:51:15+00:00</t>
+    <t>2024-02-15T15:41:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T15:41:42+00:00</t>
+    <t>2024-02-16T12:54:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T12:54:40+00:00</t>
+    <t>2024-02-16T16:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/main/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T16:35:16+00:00</t>
+    <t>2024-02-19T08:17:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
